--- a/school_1/vor_spartac_1_ceiling.xlsx
+++ b/school_1/vor_spartac_1_ceiling.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\МирзаяновИИ\Documents\projects\school_1\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="480" yWindow="30" windowWidth="19155" windowHeight="8520" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8055"/>
   </bookViews>
   <sheets>
     <sheet name="ВОРPt" sheetId="1" r:id="rId1"/>
@@ -12,7 +17,7 @@
     <sheet name="ВОР3" sheetId="4" r:id="rId3"/>
     <sheet name="Специф." sheetId="2" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -371,6 +376,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -418,7 +426,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -453,7 +461,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -805,7 +813,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="1">
-        <v>860.08</v>
+        <v>852.88</v>
       </c>
       <c r="F9">
         <v>595.26</v>
@@ -827,7 +835,7 @@
       </c>
       <c r="E10" s="1">
         <f>$E$9*D10</f>
-        <v>1118.104</v>
+        <v>1108.7440000000001</v>
       </c>
       <c r="G10" s="13"/>
     </row>
@@ -846,7 +854,7 @@
       </c>
       <c r="E11" s="1">
         <f>$E$9*D11</f>
-        <v>129.012</v>
+        <v>127.93199999999999</v>
       </c>
       <c r="G11" s="13"/>
     </row>
@@ -900,7 +908,7 @@
       </c>
       <c r="E15" s="1">
         <f>E9</f>
-        <v>860.08</v>
+        <v>852.88</v>
       </c>
       <c r="F15">
         <v>595.26</v>
@@ -922,7 +930,7 @@
       </c>
       <c r="E16" s="1">
         <f>$E$15*D16</f>
-        <v>129.012</v>
+        <v>127.93199999999999</v>
       </c>
       <c r="G16" s="14"/>
     </row>
@@ -941,7 +949,7 @@
       </c>
       <c r="E17" s="1">
         <f>$E$15*D17</f>
-        <v>3870.36</v>
+        <v>3837.96</v>
       </c>
       <c r="G17" s="14"/>
     </row>
@@ -994,7 +1002,7 @@
         <v>1</v>
       </c>
       <c r="E21" s="1">
-        <v>998.06</v>
+        <v>990.86</v>
       </c>
       <c r="F21">
         <v>746.58</v>
@@ -1016,7 +1024,7 @@
       </c>
       <c r="E22" s="1">
         <f>$E$21*D22</f>
-        <v>149.70899999999997</v>
+        <v>148.62899999999999</v>
       </c>
       <c r="G22" s="12"/>
     </row>
@@ -1035,7 +1043,7 @@
       </c>
       <c r="E23" s="1">
         <f>$E$21*D23</f>
-        <v>299.41799999999995</v>
+        <v>297.25799999999998</v>
       </c>
       <c r="G23" s="12"/>
     </row>
@@ -1825,7 +1833,7 @@
         <v>24</v>
       </c>
       <c r="C4" s="1">
-        <v>556.14</v>
+        <v>303.94</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1836,7 +1844,7 @@
         <v>23</v>
       </c>
       <c r="C5" s="1">
-        <v>303.94</v>
+        <v>548.94000000000005</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1846,7 +1854,7 @@
       </c>
       <c r="C6" s="1">
         <f>SUM(C4:C5)</f>
-        <v>860.07999999999993</v>
+        <v>852.88000000000011</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1893,7 +1901,7 @@
         <v>23</v>
       </c>
       <c r="C12" s="1">
-        <v>635.15</v>
+        <v>627.95000000000005</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1903,7 +1911,7 @@
       </c>
       <c r="C13" s="1">
         <f>SUM(C11:C12)</f>
-        <v>998.06</v>
+        <v>990.86000000000013</v>
       </c>
     </row>
   </sheetData>

--- a/school_1/vor_spartac_1_ceiling.xlsx
+++ b/school_1/vor_spartac_1_ceiling.xlsx
@@ -13,16 +13,15 @@
   </bookViews>
   <sheets>
     <sheet name="ВОРPt" sheetId="1" r:id="rId1"/>
-    <sheet name="ВОР2FB" sheetId="3" r:id="rId2"/>
-    <sheet name="ВОР3" sheetId="4" r:id="rId3"/>
-    <sheet name="Специф." sheetId="2" r:id="rId4"/>
+    <sheet name="ВОР3" sheetId="4" r:id="rId2"/>
+    <sheet name="Специф." sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="36">
   <si>
     <t>№ п.п.</t>
   </si>
@@ -72,9 +71,6 @@
     <t>Ведомость работ и используемых материалов (Шпаклевка базовая)</t>
   </si>
   <si>
-    <t>Выравнивание потолка с предварительной огрунтовкой поверхности / по ЖБ поверхности / толщ. 5 мм</t>
-  </si>
-  <si>
     <t>Шпатлевка гипсовая</t>
   </si>
   <si>
@@ -90,63 +86,12 @@
     <t>Ведомость работ и используемых материалов (Окраска)</t>
   </si>
   <si>
-    <t>Ведомость работ и используемых материалов (Файерборд)</t>
-  </si>
-  <si>
     <t>3.019</t>
   </si>
   <si>
     <t>2.022</t>
   </si>
   <si>
-    <t>шпаклевка базовая и финишная шпаклевка</t>
-  </si>
-  <si>
-    <t>Окараска</t>
-  </si>
-  <si>
-    <t>Зашивка приборов отопления / ГВЛВ / в 1 слой на каркасе (дымозащитное ограждение из Файерборда)</t>
-  </si>
-  <si>
-    <t>Ведомость работ и используемых материалов (Окраска  файерборда)</t>
-  </si>
-  <si>
-    <t>Выравнивание потолка с предварительной огрунтовкой / по оштукатуренной поверхности / толщ. 2 мм (Шпаклевка базовая)</t>
-  </si>
-  <si>
-    <t>Выравнивание поверхности с предварительной огрунтовкой</t>
-  </si>
-  <si>
-    <t>1.1</t>
-  </si>
-  <si>
-    <t>1.3</t>
-  </si>
-  <si>
-    <t>шт</t>
-  </si>
-  <si>
-    <t>пог. м</t>
-  </si>
-  <si>
-    <t>м2</t>
-  </si>
-  <si>
-    <t>Угол пластиковый_/10*15*2,5м</t>
-  </si>
-  <si>
-    <t>Профиль_/направляющий/50*50*0,40/3м</t>
-  </si>
-  <si>
-    <t>Плита Кнауф Файерборд_ / 2500х1200х12.5 м</t>
-  </si>
-  <si>
-    <t>Ведомость работ и используемых материалов (Шпаклевка финишная Файерборд)</t>
-  </si>
-  <si>
-    <t>Ведомость работ и используемых материалов (Шпаклевка базовая Файерборд)</t>
-  </si>
-  <si>
     <t>Устройство перегородок на металлическом каркасе по системе Knauf</t>
   </si>
   <si>
@@ -162,13 +107,28 @@
     <t>Краска водно-дисперсионная RAL 9003</t>
   </si>
   <si>
-    <t>Штукатурка стен сухими смесями с установкой маяков с предварительной огрунтовкой / толщ. от 16,5 мм до 21 мм</t>
-  </si>
-  <si>
     <t>Смесь цементно-песчаная М100</t>
   </si>
   <si>
     <t>Штукатурка цементная, сухая</t>
+  </si>
+  <si>
+    <t>Подготовка поверхности СКБ / потолка / ЖБ / 5 мм</t>
+  </si>
+  <si>
+    <t>Окраска поверхностей потолков с предварительной огрунтовкой поверхности / в 2 слоя</t>
+  </si>
+  <si>
+    <t>шпаклевка базовая и финишная шпаклевка потолка</t>
+  </si>
+  <si>
+    <t>Окараска потолка</t>
+  </si>
+  <si>
+    <t>Штукатурка потолка сухими смесями с установкой маяков с предварительной огрунтовкой / толщ. от 16,5 мм до 21 мм</t>
+  </si>
+  <si>
+    <t>Подготовка поверхности СКБ / потолка / ГКЛ, ПГП / 2 мм</t>
   </si>
 </sst>
 </file>
@@ -178,7 +138,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -213,16 +173,8 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFC00000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -250,12 +202,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -299,7 +245,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -341,15 +287,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
@@ -683,7 +626,7 @@
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
@@ -713,7 +656,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -731,7 +674,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>6</v>
@@ -765,11 +708,11 @@
       <c r="G5" s="15"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="23"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
+      <c r="A6" s="20"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
@@ -799,12 +742,12 @@
       </c>
       <c r="G8" s="13"/>
     </row>
-    <row r="9" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <v>1</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>5</v>
@@ -825,7 +768,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>6</v>
@@ -859,16 +802,16 @@
       <c r="G11" s="13"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
       <c r="B13" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
@@ -893,12 +836,12 @@
       </c>
       <c r="G14" s="14"/>
     </row>
-    <row r="15" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="10">
         <v>1</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>5</v>
@@ -938,7 +881,7 @@
       <c r="A17" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="19" t="s">
         <v>13</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -954,16 +897,16 @@
       <c r="G17" s="14"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="24"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
+      <c r="A18" s="21"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="6"/>
       <c r="B19" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
@@ -993,7 +936,7 @@
         <v>1</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>5</v>
@@ -1032,8 +975,8 @@
       <c r="A23" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="22" t="s">
-        <v>45</v>
+      <c r="B23" s="19" t="s">
+        <v>27</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>6</v>
@@ -1070,406 +1013,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="51" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="6"/>
-      <c r="B1" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="G1" s="21"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="21"/>
-    </row>
-    <row r="3" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="10">
-        <v>1</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="2">
-        <v>1</v>
-      </c>
-      <c r="E3" s="1">
-        <v>37.44</v>
-      </c>
-      <c r="F3" s="17"/>
-      <c r="G3" s="21"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1</v>
-      </c>
-      <c r="E4" s="1">
-        <v>22</v>
-      </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="21"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1">
-        <v>201</v>
-      </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="21"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="2">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E6" s="1">
-        <v>41.183999999999997</v>
-      </c>
-      <c r="F6" s="17"/>
-      <c r="G6" s="21"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="24"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="G7" s="21"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="6"/>
-      <c r="B8" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="G8" s="20"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="G9" s="20"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="10">
-        <v>1</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="2">
-        <v>1</v>
-      </c>
-      <c r="E10" s="1">
-        <v>37.44</v>
-      </c>
-      <c r="G10" s="20"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="2">
-        <v>1.8</v>
-      </c>
-      <c r="E11" s="1">
-        <f>E10*D11</f>
-        <v>67.391999999999996</v>
-      </c>
-      <c r="G11" s="20"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0.15</v>
-      </c>
-      <c r="E12" s="1">
-        <f>E10*D12</f>
-        <v>5.6159999999999997</v>
-      </c>
-      <c r="G12" s="20"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="23"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="G13" s="20"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="6"/>
-      <c r="B14" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="G14" s="20"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="G15" s="20"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="10">
-        <v>1</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" s="2">
-        <v>1</v>
-      </c>
-      <c r="E16" s="1">
-        <f>E10</f>
-        <v>37.44</v>
-      </c>
-      <c r="G16" s="20"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="10">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" s="2">
-        <v>0.15</v>
-      </c>
-      <c r="E17" s="1">
-        <f>E16*D17</f>
-        <v>5.6159999999999997</v>
-      </c>
-      <c r="G17" s="20"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18" s="2">
-        <v>1.8</v>
-      </c>
-      <c r="E18" s="1">
-        <f>E16*D18</f>
-        <v>67.391999999999996</v>
-      </c>
-      <c r="G18" s="20"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="24"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="G19" s="20"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="G20" s="20"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="G21" s="20"/>
-    </row>
-    <row r="22" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="10">
-        <v>1</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="2">
-        <v>1</v>
-      </c>
-      <c r="E22" s="1">
-        <v>37.44</v>
-      </c>
-      <c r="G22" s="20"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="10">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" s="2">
-        <v>0.15</v>
-      </c>
-      <c r="E23" s="1">
-        <f>E22*D23</f>
-        <v>5.6159999999999997</v>
-      </c>
-      <c r="G23" s="20"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D24" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="E24" s="1">
-        <f>E22*D24</f>
-        <v>11.231999999999999</v>
-      </c>
-      <c r="G24" s="20"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A13:E13"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1480,7 +1023,7 @@
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="7" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
@@ -1508,7 +1051,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -1521,11 +1064,11 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="24"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
+      <c r="A4" s="21"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
@@ -1558,7 +1101,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>5</v>
@@ -1575,7 +1118,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>6</v>
@@ -1607,16 +1150,16 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -1644,7 +1187,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>5</v>
@@ -1679,8 +1222,8 @@
       <c r="A15" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="22" t="s">
-        <v>17</v>
+      <c r="B15" s="19" t="s">
+        <v>16</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>6</v>
@@ -1694,16 +1237,16 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="24"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
+      <c r="A16" s="21"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
       <c r="B17" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
@@ -1731,7 +1274,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>5</v>
@@ -1765,8 +1308,8 @@
       <c r="A21" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="22" t="s">
-        <v>43</v>
+      <c r="B21" s="19" t="s">
+        <v>25</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>6</v>
@@ -1786,10 +1329,11 @@
     <mergeCell ref="A16:E16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
@@ -1801,21 +1345,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
     </row>
     <row r="2" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
+      <c r="A2" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -1826,30 +1370,30 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="18">
+      <c r="A4" s="17">
         <v>1</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1">
         <v>303.94</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="18">
+      <c r="A5" s="17">
         <v>2</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1">
         <v>548.94000000000005</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
-      <c r="B6" s="19" t="s">
+      <c r="A6" s="17"/>
+      <c r="B6" s="18" t="s">
         <v>14</v>
       </c>
       <c r="C6" s="1">
@@ -1858,21 +1402,21 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
+      <c r="A9" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -1883,30 +1427,30 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="18">
+      <c r="A11" s="17">
         <v>1</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C11" s="1">
         <v>362.91</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="18">
+      <c r="A12" s="17">
         <v>2</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C12" s="1">
         <v>627.95000000000005</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="18"/>
-      <c r="B13" s="19" t="s">
+      <c r="A13" s="17"/>
+      <c r="B13" s="18" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="1">

--- a/school_1/vor_spartac_1_ceiling.xlsx
+++ b/school_1/vor_spartac_1_ceiling.xlsx
@@ -9,19 +9,20 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8055"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8055" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="ВОРPt" sheetId="1" r:id="rId1"/>
     <sheet name="ВОР3" sheetId="4" r:id="rId2"/>
     <sheet name="Специф." sheetId="2" r:id="rId3"/>
+    <sheet name="1.032" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="37">
   <si>
     <t>№ п.п.</t>
   </si>
@@ -129,6 +130,11 @@
   </si>
   <si>
     <t>Подготовка поверхности СКБ / потолка / ГКЛ, ПГП / 2 мм</t>
+  </si>
+  <si>
+    <t>Кассетный металлический потолок Albes TEGULAR
+600х600х15 мм, кассета AP600A6/90 ̊-Т-15, цвет - белый
+RAL 9003, КМ1 - Пт4.3</t>
   </si>
 </sst>
 </file>
@@ -172,6 +178,8 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="6">
@@ -245,7 +253,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -307,6 +315,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1467,4 +1478,64 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="51" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A3" s="10">
+        <v>1</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1">
+        <v>30.09</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/school_1/vor_spartac_1_ceiling.xlsx
+++ b/school_1/vor_spartac_1_ceiling.xlsx
@@ -1529,7 +1529,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="1">
-        <v>30.09</v>
+        <v>35.299999999999997</v>
       </c>
     </row>
   </sheetData>

--- a/school_1/vor_spartac_1_ceiling.xlsx
+++ b/school_1/vor_spartac_1_ceiling.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="41">
   <si>
     <t>№ п.п.</t>
   </si>
@@ -132,9 +132,19 @@
     <t>Подготовка поверхности СКБ / потолка / ГКЛ, ПГП / 2 мм</t>
   </si>
   <si>
-    <t>Кассетный металлический потолок Albes TEGULAR
-600х600х15 мм, кассета AP600A6/90 ̊-Т-15, цвет - белый
-RAL 9003, КМ1 - Пт4.3</t>
+    <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кассетный металический потолок  </t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>м2</t>
+  </si>
+  <si>
+    <t>Монтаж подвесного потолка / типа Армстронг</t>
   </si>
 </sst>
 </file>
@@ -1482,7 +1492,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="51" customWidth="1"/>
@@ -1515,21 +1525,38 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="10">
-        <v>1</v>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>36</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
       </c>
       <c r="E3" s="1">
-        <v>35.299999999999997</v>
+        <v>32.799999999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1">
+        <v>32.799999999999997</v>
       </c>
     </row>
   </sheetData>

--- a/school_1/vor_spartac_1_ceiling.xlsx
+++ b/school_1/vor_spartac_1_ceiling.xlsx
@@ -9,20 +9,21 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8055" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8055"/>
   </bookViews>
   <sheets>
-    <sheet name="ВОРPt" sheetId="1" r:id="rId1"/>
-    <sheet name="ВОР3" sheetId="4" r:id="rId2"/>
-    <sheet name="Специф." sheetId="2" r:id="rId3"/>
-    <sheet name="1.032" sheetId="5" r:id="rId4"/>
+    <sheet name="Общий" sheetId="6" r:id="rId1"/>
+    <sheet name="ВОРPt" sheetId="1" r:id="rId2"/>
+    <sheet name="ВОР3" sheetId="4" r:id="rId3"/>
+    <sheet name="Специф." sheetId="2" r:id="rId4"/>
+    <sheet name="1.032" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="112">
   <si>
     <t>№ п.п.</t>
   </si>
@@ -145,16 +146,237 @@
   </si>
   <si>
     <t>Монтаж подвесного потолка / типа Армстронг</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.3</t>
+  </si>
+  <si>
+    <t>6.3.1.5.3</t>
+  </si>
+  <si>
+    <t>Потолки</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.3.1</t>
+  </si>
+  <si>
+    <t>6.3.1.5.3.1</t>
+  </si>
+  <si>
+    <t>Черновые работы по поверхности потолков</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.3.1.1</t>
+  </si>
+  <si>
+    <t>6.3.1.5.3.1.6.1</t>
+  </si>
+  <si>
+    <t>спорт залы №1.030 и 2.037</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.3.1.1.1</t>
+  </si>
+  <si>
+    <t>Шпатлевка цементная</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.3.1.1.2</t>
+  </si>
+  <si>
+    <t>Грунтовка БЕТОН-КОНТАКТ_/</t>
+  </si>
+  <si>
+    <t>прим. грунтовка глуб. проникновения</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.3.1.2</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.3.1.2.1</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.3.1.2.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шпатлевка финишная TERRACO HANDYCOAT ALL PURPOSE </t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.3.1.3</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.3.1.3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шпатлевка полимерная суперфинишная ЭЛИСИЛК_/белая/ PP37W </t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.3.1.3.2</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.3.1.4</t>
+  </si>
+  <si>
+    <t>пом № 2.058</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.3.1.4.1</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.3.1.4.2</t>
+  </si>
+  <si>
+    <t>Шпатлевка гипсовая_ / белая / Унифицированная по ПИК-СТАНДАРТ, 30кг</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.3.1.5</t>
+  </si>
+  <si>
+    <t>№1.007</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.3.1.5.1</t>
+  </si>
+  <si>
+    <t>помещ. №1.007</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.3.1.5.2</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.3.1.6</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.3.1.6.1</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.3.1.6.2</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.3.1.7</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.3.1.7.1</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.3.1.7.2</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.3.2</t>
+  </si>
+  <si>
+    <t>6.3.1.5.3.2</t>
+  </si>
+  <si>
+    <t>Чистовые работы по поверхности потолков</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.3.2.1</t>
+  </si>
+  <si>
+    <t>6.3.1.5.3.2.1.1</t>
+  </si>
+  <si>
+    <t>ПТ-2.2 (спорт залы №1.030, 2.037 и галерея, 2.058)</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.3.2.1.1</t>
+  </si>
+  <si>
+    <t>Краска негорючая моющаяся Protect Decor_ / RAL 9003</t>
+  </si>
+  <si>
+    <t>применительно огнестойкая Antega Строитель НГ, окраска по
+подготовленной бетонной поверхности, цвет - белый RAL
+9003, КМ0</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.3.2.1.2</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.3.2.2</t>
+  </si>
+  <si>
+    <t>помещ №1.007</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.3.2.2.1</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.3.2.2.2</t>
+  </si>
+  <si>
+    <t>прим огнестойкая Antega Строитель НГ, окраска по
+подготовленной бетонной поверхности, цвет - белый RAL
+9003, КМ0</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.4</t>
+  </si>
+  <si>
+    <t>6.3.1.5.4</t>
+  </si>
+  <si>
+    <t>Монтаж потолочных конструкций</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.4.1</t>
+  </si>
+  <si>
+    <t>6.3.1.5.4.1.6</t>
+  </si>
+  <si>
+    <t>Монтаж подвесного потолка / из акустических древесных плит</t>
+  </si>
+  <si>
+    <t>№2.058</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.4.1.1</t>
+  </si>
+  <si>
+    <t>Плита древесноволокнистая ДВП s=25мм SoundBoard SuperFine</t>
+  </si>
+  <si>
+    <t>Акустические подвесные панели из менерального
+стекловолокна горизонтальные Техносоло НГ 1200х1200 мм,
+цвет - белый, КМ1, с окраской запотолочного пространства
+цвет - белый RAL 9003, КМ0</t>
+  </si>
+  <si>
+    <t>Номер п/п</t>
+  </si>
+  <si>
+    <t>Код узла ИСР</t>
+  </si>
+  <si>
+    <t>Наименование затрат</t>
+  </si>
+  <si>
+    <t>Комментарий подрядчика</t>
+  </si>
+  <si>
+    <t>Коэф.расхода</t>
+  </si>
+  <si>
+    <t>Общее кол-во</t>
+  </si>
+  <si>
+    <t>Остаток</t>
+  </si>
+  <si>
+    <t>1.2-Пт-Э2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -191,8 +413,38 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="ГОСТ тип А"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="ГОСТ тип А"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="ГОСТ тип А"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF800000"/>
+      <name val="ГОСТ тип А"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -223,8 +475,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD8E4BC"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -258,12 +516,77 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -314,6 +637,43 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -328,6 +688,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -634,6 +997,716 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I34"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.28515625" style="20" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="20" customWidth="1"/>
+    <col min="3" max="3" width="29.42578125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="27.140625" style="20" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="20"/>
+    <col min="6" max="7" width="9.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="38" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1" s="20" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="31"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="31"/>
+    </row>
+    <row r="4" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="23">
+        <v>1</v>
+      </c>
+      <c r="G4" s="23">
+        <v>897.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="22"/>
+      <c r="C5" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="21"/>
+      <c r="E5" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="26">
+        <v>5</v>
+      </c>
+      <c r="G5" s="26">
+        <v>4487.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="22"/>
+      <c r="C6" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="26">
+        <v>0.15</v>
+      </c>
+      <c r="G6" s="26">
+        <v>134.625</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="23">
+        <v>1</v>
+      </c>
+      <c r="G7" s="23">
+        <v>897.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="22"/>
+      <c r="C8" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="21"/>
+      <c r="E8" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="26">
+        <v>0.15</v>
+      </c>
+      <c r="G8" s="26">
+        <v>134.625</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="22"/>
+      <c r="C9" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="21"/>
+      <c r="E9" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="G9" s="26">
+        <v>2243.75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="23">
+        <v>1</v>
+      </c>
+      <c r="G10" s="23">
+        <v>897.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A11" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="22"/>
+      <c r="C11" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="21"/>
+      <c r="E11" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="G11" s="26">
+        <v>1346.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="22"/>
+      <c r="C12" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="21"/>
+      <c r="E12" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" s="26">
+        <v>0.15</v>
+      </c>
+      <c r="G12" s="26">
+        <v>134.625</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="23">
+        <v>1</v>
+      </c>
+      <c r="G13" s="23">
+        <v>75.400000000000006</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="22"/>
+      <c r="C14" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="21"/>
+      <c r="E14" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" s="26">
+        <v>0.15</v>
+      </c>
+      <c r="G14" s="26">
+        <v>11.31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A15" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" s="22"/>
+      <c r="C15" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="21"/>
+      <c r="E15" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" s="26">
+        <v>4.5</v>
+      </c>
+      <c r="G15" s="26">
+        <v>339.3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A16" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16" s="23">
+        <v>1</v>
+      </c>
+      <c r="G16" s="23">
+        <v>148.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="22"/>
+      <c r="C17" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" s="26">
+        <v>5</v>
+      </c>
+      <c r="G17" s="26">
+        <v>740.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" s="22"/>
+      <c r="C18" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="21"/>
+      <c r="E18" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" s="26">
+        <v>0.15</v>
+      </c>
+      <c r="G18" s="26">
+        <v>22.215</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A19" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="F19" s="23">
+        <v>1</v>
+      </c>
+      <c r="G19" s="23">
+        <v>148.1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A20" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" s="22"/>
+      <c r="C20" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="21"/>
+      <c r="E20" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" s="26">
+        <v>0.15</v>
+      </c>
+      <c r="G20" s="26">
+        <v>22.215</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A21" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" s="22"/>
+      <c r="C21" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="21"/>
+      <c r="E21" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="G21" s="26">
+        <v>370.25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A22" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="F22" s="23">
+        <v>1</v>
+      </c>
+      <c r="G22" s="23">
+        <v>148.1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A23" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" s="22"/>
+      <c r="C23" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="21"/>
+      <c r="E23" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="G23" s="26">
+        <v>222.15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A24" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" s="22"/>
+      <c r="C24" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="21"/>
+      <c r="E24" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24" s="26">
+        <v>0.15</v>
+      </c>
+      <c r="G24" s="26">
+        <v>22.215</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="31"/>
+    </row>
+    <row r="26" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="A26" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="F26" s="23">
+        <v>1</v>
+      </c>
+      <c r="G26" s="23">
+        <v>972.9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A27" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" s="22"/>
+      <c r="C27" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="E27" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F27" s="26">
+        <v>0.3</v>
+      </c>
+      <c r="G27" s="28">
+        <v>291.87</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A28" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="22"/>
+      <c r="C28" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="21"/>
+      <c r="E28" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F28" s="26">
+        <v>0.15</v>
+      </c>
+      <c r="G28" s="28">
+        <v>145.935</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="A29" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C29" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="F29" s="23">
+        <v>1</v>
+      </c>
+      <c r="G29" s="23">
+        <v>148.1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A30" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="B30" s="22"/>
+      <c r="C30" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="21"/>
+      <c r="E30" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F30" s="26">
+        <v>0.15</v>
+      </c>
+      <c r="G30" s="28">
+        <v>22.215</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A31" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="B31" s="22"/>
+      <c r="C31" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="D31" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="E31" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F31" s="26">
+        <v>0.3</v>
+      </c>
+      <c r="G31" s="28">
+        <v>44.43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="B32" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="C32" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="31"/>
+    </row>
+    <row r="33" spans="1:7" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A33" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="C33" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="D33" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="E33" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="F33" s="23">
+        <v>1</v>
+      </c>
+      <c r="G33" s="23">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="89.25" x14ac:dyDescent="0.2">
+      <c r="A34" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="B34" s="22"/>
+      <c r="C34" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="D34" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="E34" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="F34" s="26">
+        <v>1</v>
+      </c>
+      <c r="G34" s="26">
+        <v>96.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -729,11 +1802,11 @@
       <c r="G5" s="15"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="20"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
+      <c r="A6" s="33"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
@@ -823,11 +1896,11 @@
       <c r="G11" s="13"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="20"/>
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
+      <c r="A12" s="33"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
@@ -918,11 +1991,11 @@
       <c r="G17" s="14"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="21"/>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
+      <c r="A18" s="34"/>
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="6"/>
@@ -1032,7 +2105,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1085,11 +2158,11 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="21"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
+      <c r="A4" s="34"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
@@ -1171,11 +2244,11 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="20"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
+      <c r="A10" s="33"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
@@ -1258,11 +2331,11 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="21"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
+      <c r="A16" s="34"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
@@ -1354,7 +2427,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
@@ -1366,18 +2439,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
     </row>
     <row r="2" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
@@ -1423,18 +2496,18 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
@@ -1490,7 +2563,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1500,13 +2573,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
